--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OCA GLOBAL C.B. SALOU.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OCA GLOBAL C.B. SALOU.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8663</v>
+        <v>1.7544</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3878</v>
+        <v>6.5027</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.5215</v>
+        <v>-4.7481</v>
       </c>
       <c r="G2" t="n">
         <v>8.030099999999999</v>
@@ -610,13 +610,13 @@
         <v>21.7663</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3646999999999998</v>
+        <v>-3.476500000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>4.3251</v>
+        <v>-0.5603</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.6898</v>
+        <v>-2.9166</v>
       </c>
       <c r="V2" t="n">
         <v>-6.700699999999999</v>
@@ -643,13 +643,13 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>4.739800000000001</v>
+        <v>-0.7243999999999995</v>
       </c>
       <c r="E3" t="n">
-        <v>17.147</v>
+        <v>11.7385</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.4074</v>
+        <v>-12.4632</v>
       </c>
       <c r="G3" t="n">
         <v>0.8201999999999998</v>
@@ -688,13 +688,13 @@
         <v>24.0251</v>
       </c>
       <c r="S3" t="n">
-        <v>8.7067</v>
+        <v>3.2428</v>
       </c>
       <c r="T3" t="n">
-        <v>10.3958</v>
+        <v>4.9875</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6891</v>
+        <v>-1.7449</v>
       </c>
       <c r="V3" t="n">
         <v>-5.6087</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>2.616999999999999</v>
+        <v>-1.9121</v>
       </c>
       <c r="E4" t="n">
-        <v>8.263100000000001</v>
+        <v>1.811800000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.645600000000001</v>
+        <v>-3.7243</v>
       </c>
       <c r="G4" t="n">
-        <v>-28.5665</v>
+        <v>4.947899999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.5378</v>
+        <v>4.849299999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-18.0287</v>
+        <v>0.0984999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>7.826700000000001</v>
+        <v>21.6786</v>
       </c>
       <c r="K4" t="n">
-        <v>13.2276</v>
+        <v>15.6461</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.4009</v>
+        <v>6.0324</v>
       </c>
       <c r="M4" t="n">
-        <v>-36.3933</v>
+        <v>-16.7305</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.7655</v>
+        <v>-10.7966</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.6278</v>
+        <v>-5.9337</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6429</v>
+        <v>5.3389</v>
       </c>
       <c r="Q4" t="n">
-        <v>-45.9964</v>
+        <v>-24.8465</v>
       </c>
       <c r="R4" t="n">
-        <v>44.354</v>
+        <v>30.1852</v>
       </c>
       <c r="S4" t="n">
-        <v>11.2854</v>
+        <v>-4.2887</v>
       </c>
       <c r="T4" t="n">
-        <v>5.109599999999999</v>
+        <v>-2.246</v>
       </c>
       <c r="U4" t="n">
-        <v>6.1761</v>
+        <v>-2.0429</v>
       </c>
       <c r="V4" t="n">
-        <v>21.5414</v>
+        <v>-7.910299999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>41.3233</v>
+        <v>7.225700000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.7825</v>
+        <v>-15.1359</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.3192</v>
+        <v>-2.171</v>
       </c>
       <c r="E5" t="n">
         <v>-0.1325</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1866</v>
+        <v>-2.0384</v>
       </c>
       <c r="G5" t="n">
         <v>2.4094</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1569</v>
+        <v>-0.008700000000000013</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09310000000000004</v>
+        <v>-0.09310000000000002</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0638</v>
+        <v>0.0843</v>
       </c>
       <c r="V5" t="n">
         <v>-3.9556</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>-7.124099999999999</v>
+        <v>-5.940700000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.4829</v>
+        <v>3.409000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6413000000000002</v>
+        <v>-9.35</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.6089</v>
+        <v>-28.5665</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.1597</v>
+        <v>-10.5378</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.4492</v>
+        <v>-18.0287</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9515</v>
+        <v>7.826700000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7659</v>
+        <v>13.2276</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1853</v>
+        <v>-5.4009</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.6576</v>
+        <v>-36.3933</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3937</v>
+        <v>-23.7655</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.2638</v>
+        <v>-12.6278</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8482</v>
+        <v>-1.6429</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.9815</v>
+        <v>-45.9964</v>
       </c>
       <c r="R6" t="n">
-        <v>8.829599999999999</v>
+        <v>44.354</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.5195</v>
+        <v>2.7272</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0856</v>
+        <v>0.2548999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.4338</v>
+        <v>2.4721</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1561</v>
+        <v>21.5414</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5359</v>
+        <v>41.3233</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3798</v>
+        <v>-19.7825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. MENDES KOVACS</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.209300000000001</v>
+        <v>-6.4523</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.623699999999999</v>
+        <v>-6.389699999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5854</v>
+        <v>-0.06269999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.2462</v>
+        <v>-6.6089</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.6065</v>
+        <v>-3.1597</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6394000000000001</v>
+        <v>-3.4492</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1045</v>
+        <v>-1.9515</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.0642</v>
+        <v>-1.7659</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04010000000000009</v>
+        <v>-0.1853</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1416</v>
+        <v>-4.6576</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5423</v>
+        <v>-1.3937</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5994</v>
+        <v>-3.2638</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.232</v>
+        <v>1.8482</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.1869</v>
+        <v>-6.9815</v>
       </c>
       <c r="R7" t="n">
-        <v>5.9549</v>
+        <v>8.829599999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>3.813</v>
+        <v>-2.8476</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1255</v>
+        <v>-0.9926</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3127</v>
+        <v>-1.8551</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.544</v>
+        <v>1.1561</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4579</v>
+        <v>3.5359</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.0861</v>
+        <v>-2.3798</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>K. MENDES KOVACS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.282300000000001</v>
+        <v>-9.761600000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.077099999999999</v>
+        <v>-8.375</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2053</v>
+        <v>-1.3865</v>
       </c>
       <c r="G8" t="n">
-        <v>4.947899999999999</v>
+        <v>-5.2462</v>
       </c>
       <c r="H8" t="n">
-        <v>4.849299999999999</v>
+        <v>-4.6065</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0984999999999997</v>
+        <v>-0.6394000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6786</v>
+        <v>-3.1045</v>
       </c>
       <c r="K8" t="n">
-        <v>15.6461</v>
+        <v>-3.0642</v>
       </c>
       <c r="L8" t="n">
-        <v>6.0324</v>
+        <v>-0.04010000000000009</v>
       </c>
       <c r="M8" t="n">
-        <v>-16.7305</v>
+        <v>-2.1416</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.7966</v>
+        <v>-1.5423</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.9337</v>
+        <v>-0.5994</v>
       </c>
       <c r="P8" t="n">
-        <v>5.3389</v>
+        <v>-1.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-24.8465</v>
+        <v>-7.1869</v>
       </c>
       <c r="R8" t="n">
-        <v>30.1852</v>
+        <v>5.9549</v>
       </c>
       <c r="S8" t="n">
-        <v>-10.6589</v>
+        <v>2.2607</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.1348</v>
+        <v>2.3745</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.524</v>
+        <v>-0.1139</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.910299999999999</v>
+        <v>-5.544</v>
       </c>
       <c r="W8" t="n">
-        <v>7.225700000000001</v>
+        <v>-0.4579</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.1359</v>
+        <v>-5.0861</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>-19.5085</v>
+        <v>-13.5024</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.4497</v>
+        <v>-4.8417</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.058800000000001</v>
+        <v>-8.661099999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.807700000000001</v>
+        <v>-10.1373</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3021</v>
+        <v>-15.7447</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.505700000000001</v>
+        <v>5.6071</v>
       </c>
       <c r="J9" t="n">
-        <v>13.906</v>
+        <v>26.6052</v>
       </c>
       <c r="K9" t="n">
-        <v>11.4093</v>
+        <v>7.7503</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4964</v>
+        <v>18.8549</v>
       </c>
       <c r="M9" t="n">
-        <v>-20.7138</v>
+        <v>-36.7427</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.7115</v>
+        <v>-23.4946</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.0021</v>
+        <v>-13.2477</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.08</v>
+        <v>5.7496</v>
       </c>
       <c r="Q9" t="n">
-        <v>-32.444</v>
+        <v>-44.3537</v>
       </c>
       <c r="R9" t="n">
-        <v>29.3638</v>
+        <v>50.1032</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.756500000000001</v>
+        <v>-7.1788</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.3773</v>
+        <v>-3.6388</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.3792</v>
+        <v>-3.54</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.864100000000001</v>
+        <v>-1.9362</v>
       </c>
       <c r="W9" t="n">
-        <v>7.465800000000001</v>
+        <v>16.5457</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.3299</v>
+        <v>-18.482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.1116</v>
+        <v>-15.4501</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.0379</v>
+        <v>-12.3108</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.0734</v>
+        <v>-3.139399999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1819000000000002</v>
+        <v>-6.807700000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-14.7006</v>
+        <v>-2.3021</v>
       </c>
       <c r="I10" t="n">
-        <v>14.8827</v>
+        <v>-4.505700000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>15.1838</v>
+        <v>13.906</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.1524</v>
+        <v>11.4093</v>
       </c>
       <c r="L10" t="n">
-        <v>20.3363</v>
+        <v>2.4964</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.0019</v>
+        <v>-20.7138</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.5486</v>
+        <v>-13.7115</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.4532</v>
+        <v>-7.0021</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2588</v>
+        <v>-3.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>-20.5341</v>
+        <v>-32.444</v>
       </c>
       <c r="R10" t="n">
-        <v>22.793</v>
+        <v>29.3638</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.0327</v>
+        <v>-1.6984</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8192</v>
+        <v>-1.2387</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.2135</v>
+        <v>-0.4598000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-15.5196</v>
+        <v>-3.864100000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1313</v>
+        <v>7.465800000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.651</v>
+        <v>-11.3299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-22.0816</v>
+        <v>-16.4048</v>
       </c>
       <c r="E11" t="n">
-        <v>-28.0361</v>
+        <v>-2.934100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>5.954600000000001</v>
+        <v>-13.4707</v>
       </c>
       <c r="G11" t="n">
-        <v>-24.51</v>
+        <v>3.329900000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.3574</v>
+        <v>-5.462200000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-12.1526</v>
+        <v>8.792200000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.3076</v>
+        <v>31.7245</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.448</v>
+        <v>13.6694</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.8594</v>
+        <v>18.0552</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.2025</v>
+        <v>-28.3945</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.9092</v>
+        <v>-19.1318</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.2932</v>
+        <v>-9.263</v>
       </c>
       <c r="P11" t="n">
-        <v>8.829799999999999</v>
+        <v>-14.1687</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.4541</v>
+        <v>-51.7462</v>
       </c>
       <c r="R11" t="n">
-        <v>26.2838</v>
+        <v>37.5778</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1319</v>
+        <v>-4.5488</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7383000000000002</v>
+        <v>-3.3433</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3933999999999998</v>
+        <v>-1.2053</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.269299999999999</v>
+        <v>-1.017</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4637</v>
+        <v>20.4308</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.7332</v>
+        <v>-21.448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.268</v>
+        <v>-17.1692</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.347</v>
+        <v>-6.3677</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.9209</v>
+        <v>-10.8015</v>
       </c>
       <c r="G12" t="n">
-        <v>3.329900000000002</v>
+        <v>0.1819000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.462200000000001</v>
+        <v>-14.7006</v>
       </c>
       <c r="I12" t="n">
-        <v>8.792200000000001</v>
+        <v>14.8827</v>
       </c>
       <c r="J12" t="n">
-        <v>31.7245</v>
+        <v>15.1838</v>
       </c>
       <c r="K12" t="n">
-        <v>13.6694</v>
+        <v>-5.1524</v>
       </c>
       <c r="L12" t="n">
-        <v>18.0552</v>
+        <v>20.3363</v>
       </c>
       <c r="M12" t="n">
-        <v>-28.3945</v>
+        <v>-15.0019</v>
       </c>
       <c r="N12" t="n">
-        <v>-19.1318</v>
+        <v>-9.5486</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.263</v>
+        <v>-5.4532</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.1687</v>
+        <v>2.2588</v>
       </c>
       <c r="Q12" t="n">
-        <v>-51.7462</v>
+        <v>-20.5341</v>
       </c>
       <c r="R12" t="n">
-        <v>37.5778</v>
+        <v>22.793</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.4121</v>
+        <v>-4.0905</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.7561</v>
+        <v>-1.1489</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.656</v>
+        <v>-2.9416</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.017</v>
+        <v>-15.5196</v>
       </c>
       <c r="W12" t="n">
-        <v>20.4308</v>
+        <v>0.1313</v>
       </c>
       <c r="X12" t="n">
-        <v>-21.448</v>
+        <v>-15.651</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.3104</v>
+        <v>-22.291</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.2026</v>
+        <v>-14.1527</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.107800000000001</v>
+        <v>-8.138299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-12.1511</v>
@@ -1468,13 +1468,13 @@
         <v>9.856400000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5818</v>
+        <v>0.4376</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0584</v>
+        <v>-1.0083</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4764999999999999</v>
+        <v>1.446</v>
       </c>
       <c r="V13" t="n">
         <v>-5.2385</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.1932</v>
+        <v>-22.3515</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.61</v>
+        <v>-28.6597</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5831</v>
+        <v>6.308399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.1373</v>
+        <v>-24.51</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.7447</v>
+        <v>-12.3574</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6071</v>
+        <v>-12.1526</v>
       </c>
       <c r="J14" t="n">
-        <v>26.6052</v>
+        <v>-11.3076</v>
       </c>
       <c r="K14" t="n">
-        <v>7.7503</v>
+        <v>-3.448</v>
       </c>
       <c r="L14" t="n">
-        <v>18.8549</v>
+        <v>-7.8594</v>
       </c>
       <c r="M14" t="n">
-        <v>-36.7427</v>
+        <v>-13.2025</v>
       </c>
       <c r="N14" t="n">
-        <v>-23.4946</v>
+        <v>-8.9092</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.2477</v>
+        <v>-4.2932</v>
       </c>
       <c r="P14" t="n">
-        <v>5.7496</v>
+        <v>8.829799999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-44.3537</v>
+        <v>-17.4541</v>
       </c>
       <c r="R14" t="n">
-        <v>50.1032</v>
+        <v>26.2838</v>
       </c>
       <c r="S14" t="n">
-        <v>-18.8694</v>
+        <v>-1.4017</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.4072</v>
+        <v>-1.3621</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.4621</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9362</v>
+        <v>-5.269299999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>16.5457</v>
+        <v>1.4637</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.482</v>
+        <v>-6.7332</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.6273</v>
+        <v>-26.359</v>
       </c>
       <c r="E15" t="n">
-        <v>-27.0481</v>
+        <v>-28.361</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4207</v>
+        <v>2.002099999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-7.335699999999999</v>
@@ -1624,13 +1624,13 @@
         <v>22.5879</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1078</v>
+        <v>1.3762</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8266999999999998</v>
+        <v>-0.4863000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2811</v>
+        <v>1.8623</v>
       </c>
       <c r="V15" t="n">
         <v>-12.5963</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-33.5952</v>
+        <v>-30.1912</v>
       </c>
       <c r="E16" t="n">
-        <v>-26.3963</v>
+        <v>-21.8709</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.1989</v>
+        <v>-8.320300000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-26.718</v>
@@ -1702,13 +1702,13 @@
         <v>52.9783</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.1257</v>
+        <v>-1.7218</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.5607</v>
+        <v>-2.0351</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4352</v>
+        <v>0.3134000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-15.7149</v>
@@ -1735,13 +1735,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>-47.3833</v>
+        <v>-39.7294</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.5776</v>
+        <v>-17.1034</v>
       </c>
       <c r="F17" t="n">
-        <v>-24.8053</v>
+        <v>-22.626</v>
       </c>
       <c r="G17" t="n">
         <v>-5.809799999999999</v>
@@ -1780,13 +1780,13 @@
         <v>29.5693</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.9066</v>
+        <v>-3.2529</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.375599999999999</v>
+        <v>-1.9011</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.5311</v>
+        <v>-1.3517</v>
       </c>
       <c r="V17" t="n">
         <v>-21.8368</v>
@@ -1813,22 +1813,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-254.7909</v>
+        <v>-228.6563</v>
       </c>
       <c r="E18" t="n">
-        <v>-140.2236</v>
+        <v>-128.0372</v>
       </c>
       <c r="F18" t="n">
-        <v>-114.566</v>
+        <v>-100.62</v>
       </c>
       <c r="G18" t="n">
         <v>-114.1718</v>
       </c>
       <c r="H18" t="n">
-        <v>-85.7294</v>
+        <v>-85.72940000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-28.4422</v>
+        <v>-28.44219999999999</v>
       </c>
       <c r="J18" t="n">
         <v>179.122</v>
@@ -1849,7 +1849,7 @@
         <v>-106.2195</v>
       </c>
       <c r="P18" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="Q18" t="n">
         <v>-417.8697</v>
@@ -1858,13 +1858,13 @@
         <v>417.8713</v>
       </c>
       <c r="S18" t="n">
-        <v>-50.60380000000001</v>
+        <v>-24.4699</v>
       </c>
       <c r="T18" t="n">
-        <v>-24.6236</v>
+        <v>-12.4377</v>
       </c>
       <c r="U18" t="n">
-        <v>-25.9796</v>
+        <v>-12.0337</v>
       </c>
       <c r="V18" t="n">
         <v>-90.0145</v>
